--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="418">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:00:53+00:00</t>
+    <t>2023-06-02T12:29:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,20 +304,216 @@
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-data-trace</t>
+  </si>
+  <si>
+    <t>as-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace</t>
+  </si>
+  <si>
+    <t>Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI))..</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
+    <t>HealthcareService.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -328,9 +524,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>HealthcareService.language</t>
@@ -413,31 +606,13 @@
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-healthcareservice-activity-type</t>
@@ -549,10 +724,6 @@
     <t>HealthcareService.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -560,9 +731,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -743,10 +911,6 @@
     <t>HealthcareService.name</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -866,9 +1030,6 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
   </si>
   <si>
@@ -891,25 +1052,7 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>HealthcareService.eligibility.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -1486,7 +1629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL57"/>
+  <dimension ref="A1:AL66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="81.09375" customWidth="true" bestFit="true"/>
@@ -1513,7 +1656,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="87.19921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="109.73046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1955,10 +2098,10 @@
         <v>93</v>
       </c>
       <c r="AJ4" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>73</v>
@@ -1966,10 +2109,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1986,23 +2129,21 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M5" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -2051,7 +2192,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2060,13 +2201,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
@@ -2074,21 +2215,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2100,16 +2241,16 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2135,46 +2276,46 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AC6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>73</v>
@@ -2185,11 +2326,13 @@
         <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2199,7 +2342,7 @@
         <v>81</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>73</v>
@@ -2216,9 +2359,7 @@
       <c r="M7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="N7" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>73</v>
@@ -2267,22 +2408,22 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
@@ -2290,21 +2431,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2313,19 +2454,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2375,22 +2516,22 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
@@ -2398,10 +2539,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2409,11 +2550,11 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
       </c>
@@ -2421,18 +2562,20 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>73</v>
@@ -2469,34 +2612,34 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2504,14 +2647,12 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2523,25 +2664,25 @@
         <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2597,16 +2738,16 @@
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2614,14 +2755,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2630,27 +2769,29 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2699,7 +2840,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2711,10 +2852,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2722,43 +2863,43 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2783,13 +2924,13 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>73</v>
@@ -2807,7 +2948,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2819,10 +2960,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2830,14 +2971,12 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>73</v>
       </c>
@@ -2846,27 +2985,29 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K13" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2891,13 +3032,13 @@
         <v>73</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>73</v>
@@ -2915,7 +3056,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2927,10 +3068,10 @@
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>73</v>
@@ -2938,14 +3079,12 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>73</v>
       </c>
@@ -2957,16 +3096,16 @@
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>160</v>
@@ -3025,22 +3164,22 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3048,14 +3187,12 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C15" t="s" s="2">
         <v>164</v>
       </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>73</v>
       </c>
@@ -3067,7 +3204,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>73</v>
@@ -3111,13 +3248,13 @@
         <v>73</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>73</v>
@@ -3135,22 +3272,22 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3158,46 +3295,44 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>73</v>
       </c>
@@ -3233,34 +3368,34 @@
         <v>73</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>73</v>
@@ -3268,14 +3403,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3285,25 +3420,25 @@
         <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3353,7 +3488,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3362,24 +3497,24 @@
         <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AK17" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AL17" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3390,36 +3525,32 @@
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q18" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3451,47 +3582,49 @@
         <v>73</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>190</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3509,19 +3642,19 @@
         <v>73</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3577,16 +3710,16 @@
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3597,18 +3730,20 @@
         <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -3617,7 +3752,7 @@
         <v>73</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>200</v>
@@ -3628,9 +3763,7 @@
       <c r="M20" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -3655,13 +3788,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3679,7 +3812,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3691,54 +3824,54 @@
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3763,13 +3896,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>214</v>
+        <v>73</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>215</v>
+        <v>73</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3787,7 +3920,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3799,10 +3932,10 @@
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>73</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -3810,12 +3943,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3824,7 +3959,7 @@
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -3833,20 +3968,18 @@
         <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3871,13 +4004,13 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3895,7 +4028,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3907,10 +4040,10 @@
         <v>93</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>216</v>
+        <v>73</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
@@ -3918,12 +4051,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>73</v>
       </c>
@@ -3932,28 +4067,28 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4003,7 +4138,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -4015,23 +4150,25 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>73</v>
       </c>
@@ -4040,28 +4177,28 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4111,22 +4248,22 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>73</v>
@@ -4134,44 +4271,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>73</v>
       </c>
@@ -4207,34 +4346,34 @@
         <v>73</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4242,10 +4381,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4256,28 +4395,28 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4327,33 +4466,33 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>73</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4361,37 +4500,39 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q27" s="2"/>
+      <c r="Q27" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="R27" t="s" s="2">
         <v>73</v>
       </c>
@@ -4435,7 +4576,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4447,21 +4588,21 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>252</v>
+        <v>122</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>73</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4472,28 +4613,28 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4543,22 +4684,22 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4566,42 +4707,42 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>253</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4627,13 +4768,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -4651,7 +4792,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4663,32 +4804,32 @@
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>73</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>73</v>
+        <v>264</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -4697,19 +4838,19 @@
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4735,13 +4876,13 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="Y30" t="s" s="2">
         <v>268</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -4759,7 +4900,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4771,10 +4912,10 @@
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4782,10 +4923,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4799,24 +4940,26 @@
         <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>73</v>
@@ -4841,13 +4984,13 @@
         <v>73</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>73</v>
+        <v>275</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>73</v>
+        <v>276</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4865,7 +5008,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4877,10 +5020,10 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>102</v>
+        <v>270</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -4902,7 +5045,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4911,18 +5054,20 @@
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>73</v>
@@ -4971,44 +5116,44 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>73</v>
+        <v>250</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>102</v>
+        <v>282</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>73</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -5017,19 +5162,19 @@
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5067,16 +5212,16 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>284</v>
@@ -5085,16 +5230,16 @@
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5102,46 +5247,44 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>286</v>
+        <v>73</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
@@ -5195,16 +5338,16 @@
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>95</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5212,10 +5355,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5226,7 +5369,7 @@
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -5238,16 +5381,16 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>213</v>
+        <v>298</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5273,10 +5416,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>270</v>
+        <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>293</v>
+        <v>73</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -5297,7 +5440,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5309,10 +5452,10 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5320,10 +5463,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5334,7 +5477,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -5343,19 +5486,19 @@
         <v>73</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5405,7 +5548,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5417,10 +5560,10 @@
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>305</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5428,10 +5571,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5454,16 +5597,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5489,13 +5632,13 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>270</v>
+        <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>303</v>
+        <v>73</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>304</v>
+        <v>73</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -5513,7 +5656,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5525,10 +5668,10 @@
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>312</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5536,10 +5679,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5550,10 +5693,10 @@
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>73</v>
@@ -5562,16 +5705,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5597,13 +5740,13 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>310</v>
+        <v>73</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>311</v>
+        <v>73</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -5621,7 +5764,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5633,10 +5776,10 @@
         <v>93</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5644,10 +5787,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5670,16 +5813,16 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5705,13 +5848,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>110</v>
+        <v>323</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5729,7 +5872,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5741,10 +5884,10 @@
         <v>93</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -5752,10 +5895,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5778,17 +5921,15 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>200</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -5813,13 +5954,13 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>270</v>
+        <v>73</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>320</v>
+        <v>73</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>321</v>
+        <v>73</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>73</v>
@@ -5837,7 +5978,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5849,10 +5990,10 @@
         <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>305</v>
+        <v>100</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -5860,10 +6001,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5874,7 +6015,7 @@
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -5886,13 +6027,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>323</v>
+        <v>97</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>98</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5943,7 +6084,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5952,13 +6093,13 @@
         <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>305</v>
+        <v>100</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -5966,21 +6107,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>73</v>
@@ -5992,16 +6133,16 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>274</v>
+        <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>326</v>
+        <v>104</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>327</v>
+        <v>105</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>328</v>
+        <v>106</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6039,19 +6180,19 @@
         <v>73</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6063,10 +6204,10 @@
         <v>93</v>
       </c>
       <c r="AJ42" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6074,42 +6215,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>73</v>
+        <v>332</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>73</v>
       </c>
@@ -6157,22 +6302,22 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6180,21 +6325,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -6206,16 +6351,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>128</v>
+        <v>254</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>283</v>
+        <v>338</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6241,10 +6386,10 @@
         <v>73</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>73</v>
+        <v>339</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>73</v>
@@ -6253,34 +6398,34 @@
         <v>73</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>284</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6288,46 +6433,44 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>286</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>128</v>
+        <v>295</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>288</v>
+        <v>342</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
       </c>
@@ -6375,22 +6518,22 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>95</v>
+        <v>344</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6398,10 +6541,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6412,7 +6555,7 @@
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>73</v>
@@ -6424,16 +6567,16 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6459,13 +6602,13 @@
         <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>73</v>
@@ -6483,7 +6626,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6495,10 +6638,10 @@
         <v>93</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6506,10 +6649,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6520,10 +6663,10 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>73</v>
@@ -6532,15 +6675,17 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>73</v>
@@ -6565,13 +6710,13 @@
         <v>73</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>73</v>
+        <v>357</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>73</v>
@@ -6589,22 +6734,22 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6612,10 +6757,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6626,7 +6771,7 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
@@ -6638,16 +6783,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6673,13 +6818,13 @@
         <v>73</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>73</v>
@@ -6697,22 +6842,22 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>73</v>
@@ -6720,10 +6865,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6734,7 +6879,7 @@
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>73</v>
@@ -6746,16 +6891,16 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>345</v>
+        <v>267</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6781,13 +6926,13 @@
         <v>73</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>73</v>
+        <v>367</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>73</v>
@@ -6805,22 +6950,22 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>73</v>
@@ -6828,10 +6973,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6854,13 +6999,13 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6911,22 +7056,22 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -6934,10 +7079,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6948,7 +7093,7 @@
         <v>74</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>73</v>
@@ -6960,15 +7105,17 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>231</v>
+        <v>326</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>73</v>
@@ -7017,22 +7164,22 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>280</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7040,21 +7187,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>73</v>
@@ -7066,17 +7213,15 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>282</v>
+        <v>97</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>73</v>
@@ -7113,34 +7258,34 @@
         <v>73</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>284</v>
+        <v>99</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
@@ -7148,14 +7293,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>286</v>
+        <v>102</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7168,26 +7313,24 @@
         <v>73</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>287</v>
+        <v>104</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>288</v>
+        <v>105</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>73</v>
       </c>
@@ -7223,19 +7366,19 @@
         <v>73</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7247,10 +7390,10 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>73</v>
@@ -7258,44 +7401,46 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>73</v>
+        <v>332</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>73</v>
       </c>
@@ -7343,22 +7488,22 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7366,10 +7511,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7380,7 +7525,7 @@
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>73</v>
@@ -7392,16 +7537,16 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>359</v>
+        <v>165</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>362</v>
+        <v>287</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7427,13 +7572,13 @@
         <v>73</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>73</v>
+        <v>382</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>73</v>
+        <v>383</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>73</v>
@@ -7451,22 +7596,22 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>363</v>
+        <v>122</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
@@ -7474,10 +7619,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7488,7 +7633,7 @@
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>73</v>
@@ -7500,17 +7645,15 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>73</v>
@@ -7559,7 +7702,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7571,10 +7714,10 @@
         <v>93</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
@@ -7582,10 +7725,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7596,7 +7739,7 @@
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>73</v>
@@ -7608,16 +7751,16 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>227</v>
+        <v>391</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7667,29 +7810,999 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL57">
+  <autoFilter ref="A1:AL66">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7699,7 +8812,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-healthcareservice-healthcare-activity</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-healthcareservice-healthcare-activity</t>
   </si>
   <si>
     <t>Version</t>
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AsDpHealthcareServiceHealthCareActivityProfile</t>
+    <t>AsDpHealthcareServiceHealthcareActivityProfile</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>AS Donnée Publique HealthcareService HealthCare Activity Profile</t>
+    <t>AS Donnée Publique HealthcareService Healthcare Activity Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-healthcare-activity</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-healthcare-activity</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -369,7 +369,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
 </t>
   </si>
   <si>
@@ -621,7 +621,7 @@
     <t>as-ext-healthcareservice-activity-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-activity-type}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-activity-type}
 </t>
   </si>
   <si>
@@ -641,7 +641,7 @@
     <t>as-ext-healthcareservice-authorization-date</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-date}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-date}
 </t>
   </si>
   <si>
@@ -657,7 +657,7 @@
     <t>as-ext-healthcareservice-authorization-number-arhgos</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-number-arhgos}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-number-arhgos}
 </t>
   </si>
   <si>
@@ -673,7 +673,7 @@
     <t>as-ext-healthcareservice-implementation-period</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-implementation-period}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-implementation-period}
 </t>
   </si>
   <si>
@@ -689,7 +689,7 @@
     <t>as-ext-healthcareservice-delete-autorization-implantation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-delete-autorization-implantation}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-delete-autorization-implantation}
 </t>
   </si>
   <si>
@@ -708,7 +708,7 @@
     <t>as-ext-healthcareservice-date-update-activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-date-update-activity}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-date-update-activity}
 </t>
   </si>
   <si>
@@ -787,7 +787,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1642,7 +1642,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="142.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="143.859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
